--- a/SGC-CKN/Excel/6aedab11-d12c-4e71-a18e-cda77b6d99a6_Lô_CT-02_Pd1-118_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/6aedab11-d12c-4e71-a18e-cda77b6d99a6_Lô_CT-02_Pd1-118_D800_26-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>Pd1-118</t>
+    <t>P11-118</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
